--- a/LoanOfficer-A/2023/9 Salam Sunanda Saturday.xlsx
+++ b/LoanOfficer-A/2023/9 Salam Sunanda Saturday.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>18400</v>
+        <v>19800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>5600</v>
+        <v>4200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1279,9 +1279,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45374</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
